--- a/파이썬/코딩교실/1.코딩교실준비/0.학교알리미학생수/학교알리미학생수.xlsx
+++ b/파이썬/코딩교실/1.코딩교실준비/0.학교알리미학생수/학교알리미학생수.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\0.학교알리미학생수\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실\1.코딩교실준비\0.학교알리미학생수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F93EF8-2505-426F-BE82-22AA1F4DC112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651B83DD-CDDB-48B8-83D7-B853872791D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$B$1:$C$53</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="52">
   <si>
     <t>학교명</t>
   </si>
@@ -184,166 +181,19 @@
     <t>대구화원초등학교</t>
   </si>
   <si>
-    <t>대구강북초등학교</t>
-  </si>
-  <si>
-    <t>대구경진초등학교</t>
-  </si>
-  <si>
-    <t>대구관남초등학교</t>
-  </si>
-  <si>
-    <t>대구관문초등학교</t>
-  </si>
-  <si>
-    <t>대구관음초등학교</t>
-  </si>
-  <si>
-    <t>대구관천초등학교</t>
-  </si>
-  <si>
-    <t>대구교동초등학교</t>
-  </si>
-  <si>
-    <t>대구구암초등학교</t>
-  </si>
-  <si>
-    <t>대구국우초등학교</t>
-  </si>
-  <si>
-    <t>대구달산초등학교</t>
-  </si>
-  <si>
-    <t>대구대산초등학교</t>
-  </si>
-  <si>
-    <t>대구대천초등학교</t>
-  </si>
-  <si>
-    <t>대구도남초등학교</t>
-  </si>
-  <si>
-    <t>대구동변초등학교</t>
-  </si>
-  <si>
-    <t>대구동평초등학교</t>
-  </si>
-  <si>
-    <t>대구매천초등학교</t>
-  </si>
-  <si>
-    <t>대구문성초등학교</t>
-  </si>
-  <si>
-    <t>대구복현초등학교</t>
-  </si>
-  <si>
-    <t>대구북부초등학교</t>
-  </si>
-  <si>
-    <t>대구사수초등학교</t>
-  </si>
-  <si>
-    <t>대구산격초등학교</t>
-  </si>
-  <si>
-    <t>대구삼영초등학교</t>
-  </si>
-  <si>
-    <t>대구서변초등학교</t>
-  </si>
-  <si>
-    <t>대구성북초등학교</t>
-  </si>
-  <si>
-    <t>대구신암초등학교</t>
-  </si>
-  <si>
-    <t>대구연경초등학교</t>
-  </si>
-  <si>
-    <t>대구옥산초등학교</t>
-  </si>
-  <si>
-    <t>대구운암초등학교</t>
-  </si>
-  <si>
-    <t>대구칠곡초등학교</t>
-  </si>
-  <si>
-    <t>대구칠성초등학교</t>
-  </si>
-  <si>
-    <t>대구침산초등학교</t>
-  </si>
-  <si>
-    <t>대구태암초등학교</t>
-  </si>
-  <si>
-    <t>대구태전초등학교</t>
-  </si>
-  <si>
-    <t>대구태현초등학교</t>
-  </si>
-  <si>
-    <t>대구팔달초등학교</t>
-  </si>
-  <si>
-    <t>대구학남초등학교</t>
-  </si>
-  <si>
-    <t>대구학정초등학교</t>
-  </si>
-  <si>
-    <t>대구함지초등학교</t>
-  </si>
-  <si>
-    <t>북대구초등학교</t>
-  </si>
-  <si>
-    <t>학급</t>
-  </si>
-  <si>
-    <t>강북중학교</t>
-  </si>
-  <si>
-    <t>관천중학교</t>
-  </si>
-  <si>
-    <t>구암중학교</t>
-  </si>
-  <si>
-    <t>대구북중학교</t>
-  </si>
-  <si>
-    <t>동변중학교</t>
-  </si>
-  <si>
-    <t>동평중학교</t>
-  </si>
-  <si>
-    <t>매천중학교</t>
-  </si>
-  <si>
-    <t>복현중학교</t>
-  </si>
-  <si>
-    <t>사수중학교</t>
-  </si>
-  <si>
-    <t>성광중학교</t>
-  </si>
-  <si>
-    <t>칠곡중학교</t>
-  </si>
-  <si>
-    <t>침산중학교</t>
-  </si>
-  <si>
-    <t>학남중학교</t>
-  </si>
-  <si>
     <t>계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학급수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -391,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -425,6 +275,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -434,7 +321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -452,6 +339,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2313,7 +2212,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
@@ -2325,7 +2224,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -3356,7 +3255,7 @@
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="E35">
         <f>SUM(E2:E34)</f>
@@ -3365,7 +3264,7 @@
       <c r="F35"/>
       <c r="G35"/>
       <c r="H35" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="I35">
         <f>SUM(I2:I34)</f>
@@ -3445,443 +3344,1294 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:C53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8D81D3-D650-463D-B98B-14BE1AEC6353}">
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7">
+        <v>15</v>
+      </c>
+      <c r="C2" s="7">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
+        <v>2</v>
+      </c>
+      <c r="J2" s="7">
+        <f>SUM(B2:E2)</f>
+        <v>62</v>
+      </c>
+      <c r="K2" s="7">
+        <f>SUM(F2:I2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7">
+        <v>118</v>
+      </c>
+      <c r="C3" s="7">
+        <v>143</v>
+      </c>
+      <c r="D3" s="7">
+        <v>156</v>
+      </c>
+      <c r="E3" s="7">
+        <v>163</v>
+      </c>
+      <c r="F3" s="7">
+        <v>5</v>
+      </c>
+      <c r="G3" s="7">
+        <v>6</v>
+      </c>
+      <c r="H3" s="7">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7">
+        <v>7</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" ref="J3:J34" si="0">SUM(B3:E3)</f>
+        <v>580</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K34" si="1">SUM(F3:I3)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7">
+        <v>62</v>
+      </c>
+      <c r="C4" s="7">
+        <v>82</v>
+      </c>
+      <c r="D4" s="7">
+        <v>83</v>
+      </c>
+      <c r="E4" s="7">
+        <v>72</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7">
+        <v>4</v>
+      </c>
+      <c r="H4" s="7">
+        <v>4</v>
+      </c>
+      <c r="I4" s="7">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" si="0"/>
+        <v>299</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7">
+        <v>16</v>
+      </c>
+      <c r="E5" s="7">
+        <v>19</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7">
+        <v>25</v>
+      </c>
+      <c r="E6" s="7">
+        <v>26</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7">
+        <v>2</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="7">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="7">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7">
+        <v>24</v>
+      </c>
+      <c r="D8" s="7">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2</v>
+      </c>
+      <c r="H8" s="7">
+        <v>2</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7">
+        <v>146</v>
+      </c>
+      <c r="C9" s="7">
+        <v>149</v>
+      </c>
+      <c r="D9" s="7">
+        <v>158</v>
+      </c>
+      <c r="E9" s="7">
+        <v>176</v>
+      </c>
+      <c r="F9" s="7">
+        <v>7</v>
+      </c>
+      <c r="G9" s="7">
+        <v>6</v>
+      </c>
+      <c r="H9" s="7">
+        <v>6</v>
+      </c>
+      <c r="I9" s="7">
+        <v>7</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="0"/>
+        <v>629</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7">
+        <v>116</v>
+      </c>
+      <c r="C10" s="7">
+        <v>145</v>
+      </c>
+      <c r="D10" s="7">
+        <v>182</v>
+      </c>
+      <c r="E10" s="7">
+        <v>217</v>
+      </c>
+      <c r="F10" s="7">
+        <v>5</v>
+      </c>
+      <c r="G10" s="7">
+        <v>6</v>
+      </c>
+      <c r="H10" s="7">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7">
+        <v>43</v>
+      </c>
+      <c r="D11" s="7">
+        <v>39</v>
+      </c>
+      <c r="E11" s="7">
+        <v>53</v>
+      </c>
+      <c r="F11" s="7">
+        <v>2</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="7">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7">
+        <v>7</v>
+      </c>
+      <c r="E12" s="7">
+        <v>7</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7">
+        <v>49</v>
+      </c>
+      <c r="C13" s="7">
+        <v>62</v>
+      </c>
+      <c r="D13" s="7">
+        <v>66</v>
+      </c>
+      <c r="E13" s="7">
+        <v>77</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7">
+        <v>3</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>3</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="0"/>
+        <v>254</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="7">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7">
+        <v>12</v>
+      </c>
+      <c r="D14" s="7">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>25</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="7">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7">
+        <v>4</v>
+      </c>
+      <c r="E15" s="7">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7">
+        <v>1</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="7">
+        <v>33</v>
+      </c>
+      <c r="C16" s="7">
+        <v>32</v>
+      </c>
+      <c r="D16" s="7">
+        <v>27</v>
+      </c>
+      <c r="E16" s="7">
+        <v>39</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2</v>
+      </c>
+      <c r="G16" s="7">
+        <v>2</v>
+      </c>
+      <c r="H16" s="7">
+        <v>2</v>
+      </c>
+      <c r="I16" s="7">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="7">
+        <v>112</v>
+      </c>
+      <c r="C17" s="7">
+        <v>145</v>
+      </c>
+      <c r="D17" s="7">
+        <v>166</v>
+      </c>
+      <c r="E17" s="7">
+        <v>183</v>
+      </c>
+      <c r="F17" s="7">
+        <v>5</v>
+      </c>
+      <c r="G17" s="7">
+        <v>6</v>
+      </c>
+      <c r="H17" s="7">
+        <v>7</v>
+      </c>
+      <c r="I17" s="7">
+        <v>8</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="0"/>
+        <v>606</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="7">
+        <v>206</v>
+      </c>
+      <c r="C18" s="7">
+        <v>205</v>
+      </c>
+      <c r="D18" s="7">
+        <v>231</v>
+      </c>
+      <c r="E18" s="7">
+        <v>193</v>
+      </c>
+      <c r="F18" s="7">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7">
+        <v>8</v>
+      </c>
+      <c r="H18" s="7">
+        <v>9</v>
+      </c>
+      <c r="I18" s="7">
+        <v>8</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="0"/>
+        <v>835</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7">
+        <v>61</v>
+      </c>
+      <c r="C19" s="7">
+        <v>86</v>
+      </c>
+      <c r="D19" s="7">
+        <v>99</v>
+      </c>
+      <c r="E19" s="7">
+        <v>89</v>
+      </c>
+      <c r="F19" s="7">
+        <v>3</v>
+      </c>
+      <c r="G19" s="7">
+        <v>4</v>
+      </c>
+      <c r="H19" s="7">
+        <v>4</v>
+      </c>
+      <c r="I19" s="7">
+        <v>4</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="0"/>
+        <v>335</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="7">
+        <v>197</v>
+      </c>
+      <c r="C20" s="7">
+        <v>247</v>
+      </c>
+      <c r="D20" s="7">
+        <v>237</v>
+      </c>
+      <c r="E20" s="7">
+        <v>259</v>
+      </c>
+      <c r="F20" s="7">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2">
+      <c r="H20" s="7">
+        <v>10</v>
+      </c>
+      <c r="I20" s="7">
+        <v>10</v>
+      </c>
+      <c r="J20" s="7">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B21" s="7">
+        <v>252</v>
+      </c>
+      <c r="C21" s="7">
+        <v>209</v>
+      </c>
+      <c r="D21" s="7">
+        <v>218</v>
+      </c>
+      <c r="E21" s="7">
+        <v>221</v>
+      </c>
+      <c r="F21" s="7">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7">
+        <v>8</v>
+      </c>
+      <c r="H21" s="7">
+        <v>9</v>
+      </c>
+      <c r="I21" s="7">
+        <v>9</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="7">
+        <v>34</v>
+      </c>
+      <c r="C22" s="7">
+        <v>36</v>
+      </c>
+      <c r="D22" s="7">
+        <v>42</v>
+      </c>
+      <c r="E22" s="7">
+        <v>36</v>
+      </c>
+      <c r="F22" s="7">
+        <v>2</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2</v>
+      </c>
+      <c r="H22" s="7">
+        <v>2</v>
+      </c>
+      <c r="I22" s="7">
+        <v>2</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="0"/>
+        <v>148</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="7">
+        <v>62</v>
+      </c>
+      <c r="C23" s="7">
+        <v>74</v>
+      </c>
+      <c r="D23" s="7">
+        <v>93</v>
+      </c>
+      <c r="E23" s="7">
+        <v>105</v>
+      </c>
+      <c r="F23" s="7">
+        <v>3</v>
+      </c>
+      <c r="G23" s="7">
+        <v>3</v>
+      </c>
+      <c r="H23" s="7">
+        <v>4</v>
+      </c>
+      <c r="I23" s="7">
+        <v>4</v>
+      </c>
+      <c r="J23" s="7">
+        <f t="shared" si="0"/>
+        <v>334</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="7">
+        <v>43</v>
+      </c>
+      <c r="C24" s="7">
+        <v>53</v>
+      </c>
+      <c r="D24" s="7">
+        <v>69</v>
+      </c>
+      <c r="E24" s="7">
+        <v>55</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7">
+        <v>3</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>3</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="7">
+        <v>217</v>
+      </c>
+      <c r="C25" s="7">
+        <v>273</v>
+      </c>
+      <c r="D25" s="7">
+        <v>273</v>
+      </c>
+      <c r="E25" s="7">
+        <v>281</v>
+      </c>
+      <c r="F25" s="7">
+        <v>9</v>
+      </c>
+      <c r="G25" s="7">
+        <v>10</v>
+      </c>
+      <c r="H25" s="7">
+        <v>10</v>
+      </c>
+      <c r="I25" s="7">
+        <v>11</v>
+      </c>
+      <c r="J25" s="7">
+        <f t="shared" si="0"/>
+        <v>1044</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="7">
         <v>89</v>
       </c>
-      <c r="C3">
+      <c r="C26" s="7">
+        <v>74</v>
+      </c>
+      <c r="D26" s="7">
+        <v>95</v>
+      </c>
+      <c r="E26" s="7">
+        <v>117</v>
+      </c>
+      <c r="F26" s="7">
+        <v>4</v>
+      </c>
+      <c r="G26" s="7">
+        <v>4</v>
+      </c>
+      <c r="H26" s="7">
+        <v>4</v>
+      </c>
+      <c r="I26" s="7">
+        <v>5</v>
+      </c>
+      <c r="J26" s="7">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="7">
+        <v>22</v>
+      </c>
+      <c r="C27" s="7">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7">
+        <v>31</v>
+      </c>
+      <c r="E27" s="7">
+        <v>22</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7">
+        <v>1</v>
+      </c>
+      <c r="H27" s="7">
+        <v>2</v>
+      </c>
+      <c r="I27" s="7">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="7">
+        <v>98</v>
+      </c>
+      <c r="C28" s="7">
+        <v>92</v>
+      </c>
+      <c r="D28" s="7">
+        <v>68</v>
+      </c>
+      <c r="E28" s="7">
+        <v>71</v>
+      </c>
+      <c r="F28" s="7">
+        <v>5</v>
+      </c>
+      <c r="G28" s="7">
+        <v>4</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>3</v>
+      </c>
+      <c r="J28" s="7">
+        <f t="shared" si="0"/>
+        <v>329</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="7">
+        <v>121</v>
+      </c>
+      <c r="C29" s="7">
+        <v>142</v>
+      </c>
+      <c r="D29" s="7">
+        <v>169</v>
+      </c>
+      <c r="E29" s="7">
+        <v>160</v>
+      </c>
+      <c r="F29" s="7">
+        <v>5</v>
+      </c>
+      <c r="G29" s="7">
+        <v>6</v>
+      </c>
+      <c r="H29" s="7">
+        <v>7</v>
+      </c>
+      <c r="I29" s="7">
+        <v>7</v>
+      </c>
+      <c r="J29" s="7">
+        <f t="shared" si="0"/>
+        <v>592</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="7">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="D30" s="7">
+        <v>15</v>
+      </c>
+      <c r="E30" s="7">
+        <v>10</v>
+      </c>
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1</v>
+      </c>
+      <c r="I30" s="7">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="K30" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="7">
+        <v>30</v>
+      </c>
+      <c r="C31" s="7">
+        <v>29</v>
+      </c>
+      <c r="D31" s="7">
+        <v>45</v>
+      </c>
+      <c r="E31" s="7">
+        <v>49</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>2</v>
+      </c>
+      <c r="H31" s="7">
+        <v>2</v>
+      </c>
+      <c r="I31" s="7">
+        <v>3</v>
+      </c>
+      <c r="J31" s="7">
+        <f t="shared" si="0"/>
+        <v>153</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="7">
+        <v>77</v>
+      </c>
+      <c r="C32" s="7">
+        <v>65</v>
+      </c>
+      <c r="D32" s="7">
+        <v>71</v>
+      </c>
+      <c r="E32" s="7">
+        <v>66</v>
+      </c>
+      <c r="F32" s="7">
+        <v>4</v>
+      </c>
+      <c r="G32" s="7">
+        <v>3</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>3</v>
+      </c>
+      <c r="J32" s="7">
+        <f t="shared" si="0"/>
+        <v>279</v>
+      </c>
+      <c r="K32" s="7">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="7">
+        <v>31</v>
+      </c>
+      <c r="C33" s="7">
+        <v>43</v>
+      </c>
+      <c r="D33" s="7">
+        <v>43</v>
+      </c>
+      <c r="E33" s="7">
+        <v>37</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2</v>
+      </c>
+      <c r="G33" s="7">
+        <v>2</v>
+      </c>
+      <c r="H33" s="7">
+        <v>2</v>
+      </c>
+      <c r="I33" s="7">
+        <v>2</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" si="0"/>
+        <v>154</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="7">
+        <v>61</v>
+      </c>
+      <c r="C34" s="7">
+        <v>58</v>
+      </c>
+      <c r="D34" s="7">
+        <v>59</v>
+      </c>
+      <c r="E34" s="7">
+        <v>73</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="7">
+        <v>3</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
+        <v>3</v>
+      </c>
+      <c r="J34" s="7">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53">
-        <v>28</v>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="7">
+        <f>SUM(J2:J34)</f>
+        <v>10894</v>
+      </c>
+      <c r="K35" s="7">
+        <f>SUM(K2:K34)</f>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:C53" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C53">
-      <sortCondition ref="B1:B53"/>
-    </sortState>
-  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="A35:I35"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
